--- a/artfynd/A 73321-2021 artfynd.xlsx
+++ b/artfynd/A 73321-2021 artfynd.xlsx
@@ -675,52 +675,49 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129678315</v>
+        <v>129678392</v>
       </c>
       <c r="B2" t="n">
-        <v>80220</v>
+        <v>98768</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>229504</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grynig filtlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Peltigera collina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Schrad.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>35</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Holmtorp, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>467444</v>
+        <v>467476</v>
       </c>
       <c r="R2" t="n">
-        <v>6572961</v>
+        <v>6572930</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -761,78 +758,70 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>Emilia Sundell</t>
+        </is>
+      </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Hannes Byström</t>
+          <t>Emilia Sundell</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129678392</v>
+        <v>129678315</v>
       </c>
       <c r="B3" t="n">
-        <v>98756</v>
+        <v>80225</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>229504</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grynig filtlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Peltigera collina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Schrad.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>35</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Holmtorp, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>467476</v>
+        <v>467444</v>
       </c>
       <c r="R3" t="n">
-        <v>6572930</v>
+        <v>6572961</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -873,10 +862,36 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
       <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Emilia Sundell</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Emilia Sundell, Hannes Byström</t>
+        </is>
+      </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
@@ -884,7 +899,7 @@
         <v>129678322</v>
       </c>
       <c r="B4" t="n">
-        <v>58447</v>
+        <v>58452</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -973,9 +988,14 @@
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Emilia Sundell</t>
+        </is>
+      </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Hannes Byström</t>
+          <t>Emilia Sundell, Hannes Byström</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -985,7 +1005,7 @@
         <v>129678393</v>
       </c>
       <c r="B5" t="n">
-        <v>58447</v>
+        <v>58452</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1069,6 +1089,16 @@
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Emilia Sundell</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Emilia Sundell</t>
+        </is>
+      </c>
       <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>

--- a/artfynd/A 73321-2021 artfynd.xlsx
+++ b/artfynd/A 73321-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129678392</v>
       </c>
       <c r="B2" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>129678315</v>
       </c>
       <c r="B3" t="n">
-        <v>80225</v>
+        <v>80226</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>129678322</v>
       </c>
       <c r="B4" t="n">
-        <v>58452</v>
+        <v>58453</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
         <v>129678393</v>
       </c>
       <c r="B5" t="n">
-        <v>58452</v>
+        <v>58453</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 73321-2021 artfynd.xlsx
+++ b/artfynd/A 73321-2021 artfynd.xlsx
@@ -675,49 +675,52 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129678392</v>
+        <v>129678315</v>
       </c>
       <c r="B2" t="n">
-        <v>98769</v>
+        <v>80231</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>229504</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grynig filtlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Peltigera collina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Schrad.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>35</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Holmtorp, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>467476</v>
+        <v>467444</v>
       </c>
       <c r="R2" t="n">
-        <v>6572930</v>
+        <v>6572961</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -758,9 +761,25 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
@@ -769,59 +788,56 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Emilia Sundell</t>
+          <t>Emilia Sundell, Hannes Byström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129678315</v>
+        <v>129678392</v>
       </c>
       <c r="B3" t="n">
-        <v>80226</v>
+        <v>98774</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229504</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grynig filtlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Peltigera collina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Schrad.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>35</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Holmtorp, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>467444</v>
+        <v>467476</v>
       </c>
       <c r="R3" t="n">
-        <v>6572961</v>
+        <v>6572930</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -862,25 +878,9 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
@@ -889,7 +889,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Emilia Sundell, Hannes Byström</t>
+          <t>Emilia Sundell</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 73321-2021 artfynd.xlsx
+++ b/artfynd/A 73321-2021 artfynd.xlsx
@@ -675,52 +675,49 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129678315</v>
+        <v>129678392</v>
       </c>
       <c r="B2" t="n">
-        <v>80231</v>
+        <v>98774</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>229504</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grynig filtlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Peltigera collina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Schrad.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>35</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Holmtorp, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>467444</v>
+        <v>467476</v>
       </c>
       <c r="R2" t="n">
-        <v>6572961</v>
+        <v>6572930</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -761,25 +758,9 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
@@ -788,56 +769,59 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Emilia Sundell, Hannes Byström</t>
+          <t>Emilia Sundell</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129678392</v>
+        <v>129678315</v>
       </c>
       <c r="B3" t="n">
-        <v>98774</v>
+        <v>80231</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>229504</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grynig filtlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Peltigera collina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Schrad.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>35</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Holmtorp, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>467476</v>
+        <v>467444</v>
       </c>
       <c r="R3" t="n">
-        <v>6572930</v>
+        <v>6572961</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -878,9 +862,25 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
@@ -889,7 +889,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Emilia Sundell</t>
+          <t>Emilia Sundell, Hannes Byström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 73321-2021 artfynd.xlsx
+++ b/artfynd/A 73321-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129678392</v>
       </c>
       <c r="B2" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 73321-2021 artfynd.xlsx
+++ b/artfynd/A 73321-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129678392</v>
       </c>
       <c r="B2" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 73321-2021 artfynd.xlsx
+++ b/artfynd/A 73321-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1101,6 +1101,121 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>129896162</v>
+      </c>
+      <c r="B6" t="n">
+        <v>98785</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Holmtorp, ONO om, Vrm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>467477</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6572930</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>T-Deg-7038</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-06-27</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-06-27</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Owe Nilsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Emilia Sundell</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 73321-2021 artfynd.xlsx
+++ b/artfynd/A 73321-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129678392</v>
       </c>
       <c r="B2" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>129896162</v>
       </c>
       <c r="B6" t="n">
-        <v>98785</v>
+        <v>98790</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 73321-2021 artfynd.xlsx
+++ b/artfynd/A 73321-2021 artfynd.xlsx
@@ -675,49 +675,52 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129678392</v>
+        <v>129678315</v>
       </c>
       <c r="B2" t="n">
-        <v>98790</v>
+        <v>80231</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>229504</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grynig filtlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Peltigera collina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Schrad.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>35</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Holmtorp, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>467476</v>
+        <v>467444</v>
       </c>
       <c r="R2" t="n">
-        <v>6572930</v>
+        <v>6572961</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -758,8 +761,24 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -769,59 +788,56 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Emilia Sundell</t>
+          <t>Emilia Sundell, Hannes Byström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129678315</v>
+        <v>129678392</v>
       </c>
       <c r="B3" t="n">
-        <v>80231</v>
+        <v>98790</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229504</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grynig filtlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Peltigera collina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Schrad.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>35</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Holmtorp, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>467444</v>
+        <v>467476</v>
       </c>
       <c r="R3" t="n">
-        <v>6572961</v>
+        <v>6572930</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -862,24 +878,8 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Emilia Sundell, Hannes Byström</t>
+          <t>Emilia Sundell</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 73321-2021 artfynd.xlsx
+++ b/artfynd/A 73321-2021 artfynd.xlsx
@@ -675,52 +675,49 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129678315</v>
+        <v>129678392</v>
       </c>
       <c r="B2" t="n">
-        <v>80231</v>
+        <v>98790</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>229504</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grynig filtlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Peltigera collina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Schrad.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>35</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Holmtorp, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>467444</v>
+        <v>467476</v>
       </c>
       <c r="R2" t="n">
-        <v>6572961</v>
+        <v>6572930</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -761,24 +758,8 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -788,56 +769,59 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Emilia Sundell, Hannes Byström</t>
+          <t>Emilia Sundell</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129678392</v>
+        <v>129678315</v>
       </c>
       <c r="B3" t="n">
-        <v>98790</v>
+        <v>80231</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>229504</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grynig filtlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Peltigera collina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Schrad.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>35</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Holmtorp, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>467476</v>
+        <v>467444</v>
       </c>
       <c r="R3" t="n">
-        <v>6572930</v>
+        <v>6572961</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -878,8 +862,24 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Emilia Sundell</t>
+          <t>Emilia Sundell, Hannes Byström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -1106,7 +1106,7 @@
         <v>129896162</v>
       </c>
       <c r="B6" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 73321-2021 artfynd.xlsx
+++ b/artfynd/A 73321-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129678392</v>
       </c>
       <c r="B2" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>129678315</v>
       </c>
       <c r="B3" t="n">
-        <v>80231</v>
+        <v>80234</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>129678322</v>
       </c>
       <c r="B4" t="n">
-        <v>58453</v>
+        <v>58456</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
         <v>129678393</v>
       </c>
       <c r="B5" t="n">
-        <v>58453</v>
+        <v>58456</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 73321-2021 artfynd.xlsx
+++ b/artfynd/A 73321-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129678392</v>
       </c>
       <c r="B2" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>129678315</v>
       </c>
       <c r="B3" t="n">
-        <v>80234</v>
+        <v>80237</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>129678322</v>
       </c>
       <c r="B4" t="n">
-        <v>58456</v>
+        <v>58459</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
         <v>129678393</v>
       </c>
       <c r="B5" t="n">
-        <v>58456</v>
+        <v>58459</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>129896162</v>
       </c>
       <c r="B6" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 73321-2021 artfynd.xlsx
+++ b/artfynd/A 73321-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129678392</v>
       </c>
       <c r="B2" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>129678315</v>
       </c>
       <c r="B3" t="n">
-        <v>80237</v>
+        <v>80238</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>129896162</v>
       </c>
       <c r="B6" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 73321-2021 artfynd.xlsx
+++ b/artfynd/A 73321-2021 artfynd.xlsx
@@ -675,49 +675,52 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129678392</v>
+        <v>129678315</v>
       </c>
       <c r="B2" t="n">
-        <v>98798</v>
+        <v>80238</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>229504</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grynig filtlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Peltigera collina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Schrad.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>35</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Holmtorp, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>467476</v>
+        <v>467444</v>
       </c>
       <c r="R2" t="n">
-        <v>6572930</v>
+        <v>6572961</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -758,8 +761,24 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -769,59 +788,56 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Emilia Sundell</t>
+          <t>Emilia Sundell, Hannes Byström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129678315</v>
+        <v>129678392</v>
       </c>
       <c r="B3" t="n">
-        <v>80238</v>
+        <v>98798</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229504</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grynig filtlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Peltigera collina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Schrad.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>35</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Holmtorp, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>467444</v>
+        <v>467476</v>
       </c>
       <c r="R3" t="n">
-        <v>6572961</v>
+        <v>6572930</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -862,24 +878,8 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Emilia Sundell, Hannes Byström</t>
+          <t>Emilia Sundell</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 73321-2021 artfynd.xlsx
+++ b/artfynd/A 73321-2021 artfynd.xlsx
@@ -675,52 +675,49 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129678315</v>
+        <v>129678392</v>
       </c>
       <c r="B2" t="n">
-        <v>80238</v>
+        <v>98798</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>229504</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grynig filtlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Peltigera collina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Schrad.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>35</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Holmtorp, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>467444</v>
+        <v>467476</v>
       </c>
       <c r="R2" t="n">
-        <v>6572961</v>
+        <v>6572930</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -761,24 +758,8 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -788,56 +769,59 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Emilia Sundell, Hannes Byström</t>
+          <t>Emilia Sundell</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129678392</v>
+        <v>129678315</v>
       </c>
       <c r="B3" t="n">
-        <v>98798</v>
+        <v>80238</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>229504</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grynig filtlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Peltigera collina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Schrad.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>35</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Holmtorp, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>467476</v>
+        <v>467444</v>
       </c>
       <c r="R3" t="n">
-        <v>6572930</v>
+        <v>6572961</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -878,8 +862,24 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Emilia Sundell</t>
+          <t>Emilia Sundell, Hannes Byström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 73321-2021 artfynd.xlsx
+++ b/artfynd/A 73321-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129678392</v>
       </c>
       <c r="B2" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>129678315</v>
       </c>
       <c r="B3" t="n">
-        <v>80238</v>
+        <v>80239</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>129678322</v>
       </c>
       <c r="B4" t="n">
-        <v>58459</v>
+        <v>58460</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
         <v>129678393</v>
       </c>
       <c r="B5" t="n">
-        <v>58459</v>
+        <v>58460</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>129896162</v>
       </c>
       <c r="B6" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 73321-2021 artfynd.xlsx
+++ b/artfynd/A 73321-2021 artfynd.xlsx
@@ -1106,7 +1106,7 @@
         <v>129896162</v>
       </c>
       <c r="B6" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 73321-2021 artfynd.xlsx
+++ b/artfynd/A 73321-2021 artfynd.xlsx
@@ -1106,7 +1106,7 @@
         <v>129896162</v>
       </c>
       <c r="B6" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 73321-2021 artfynd.xlsx
+++ b/artfynd/A 73321-2021 artfynd.xlsx
@@ -1106,7 +1106,7 @@
         <v>129896162</v>
       </c>
       <c r="B6" t="n">
-        <v>99019</v>
+        <v>99021</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 73321-2021 artfynd.xlsx
+++ b/artfynd/A 73321-2021 artfynd.xlsx
@@ -1106,7 +1106,7 @@
         <v>129896162</v>
       </c>
       <c r="B6" t="n">
-        <v>99021</v>
+        <v>99022</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 73321-2021 artfynd.xlsx
+++ b/artfynd/A 73321-2021 artfynd.xlsx
@@ -1106,7 +1106,7 @@
         <v>129896162</v>
       </c>
       <c r="B6" t="n">
-        <v>99022</v>
+        <v>99023</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 73321-2021 artfynd.xlsx
+++ b/artfynd/A 73321-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1216,6 +1216,104 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>131521663</v>
+      </c>
+      <c r="B7" t="n">
+        <v>92277</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Holmtorp, Karlskoga, Vrm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>467244</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6572972</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Mattias Drejby</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Mattias Drejby</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 73321-2021 artfynd.xlsx
+++ b/artfynd/A 73321-2021 artfynd.xlsx
@@ -1106,7 +1106,7 @@
         <v>129896162</v>
       </c>
       <c r="B6" t="n">
-        <v>99023</v>
+        <v>99026</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1221,7 +1221,7 @@
         <v>131521663</v>
       </c>
       <c r="B7" t="n">
-        <v>92277</v>
+        <v>92280</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 73321-2021 artfynd.xlsx
+++ b/artfynd/A 73321-2021 artfynd.xlsx
@@ -1106,7 +1106,7 @@
         <v>129896162</v>
       </c>
       <c r="B6" t="n">
-        <v>99026</v>
+        <v>99027</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1221,7 +1221,7 @@
         <v>131521663</v>
       </c>
       <c r="B7" t="n">
-        <v>92280</v>
+        <v>92281</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 73321-2021 artfynd.xlsx
+++ b/artfynd/A 73321-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,52 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129678392</v>
+        <v>131521663</v>
       </c>
       <c r="B2" t="n">
-        <v>98815</v>
+        <v>92369</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Holmtorp, Vrm</t>
+          <t>Holmtorp, Karlskoga, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>467476</v>
+        <v>467244</v>
       </c>
       <c r="R2" t="n">
-        <v>6572930</v>
+        <v>6572972</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -744,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -758,70 +754,64 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Emilia Sundell</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Emilia Sundell</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129678315</v>
+        <v>131507935</v>
       </c>
       <c r="B3" t="n">
-        <v>80239</v>
+        <v>91872</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229504</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grynig filtlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Peltigera collina</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Schrad.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Holmtorp, Vrm</t>
+          <t>Holmtorp, Holmtorp, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>467444</v>
+        <v>467374</v>
       </c>
       <c r="R3" t="n">
-        <v>6572961</v>
+        <v>6572837</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -848,12 +838,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -862,88 +862,68 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Emilia Sundell</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Emilia Sundell, Hannes Byström</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129678322</v>
+        <v>131509684</v>
       </c>
       <c r="B4" t="n">
-        <v>58460</v>
+        <v>57950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103055</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Holmtorp, Vrm</t>
+          <t>Holmtorp, Holmtorp, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>467351</v>
+        <v>467374</v>
       </c>
       <c r="R4" t="n">
-        <v>6573239</v>
+        <v>6572837</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -970,12 +950,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -990,22 +980,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Emilia Sundell</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Emilia Sundell, Hannes Byström</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129678393</v>
+        <v>129678322</v>
       </c>
       <c r="B5" t="n">
-        <v>58460</v>
+        <v>58676</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1035,16 +1025,21 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Holmtorp, Vrm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>467216</v>
+        <v>467351</v>
       </c>
       <c r="R5" t="n">
-        <v>6573386</v>
+        <v>6573239</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1096,64 +1091,59 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Emilia Sundell</t>
+          <t>Emilia Sundell, Hannes Byström</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129896162</v>
+        <v>129678393</v>
       </c>
       <c r="B6" t="n">
-        <v>99038</v>
+        <v>58676</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>103055</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Holmtorp, ONO om, Vrm</t>
+          <t>Holmtorp, Vrm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>467477</v>
+        <v>467216</v>
       </c>
       <c r="R6" t="n">
-        <v>6572930</v>
+        <v>6573386</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1173,11 +1163,6 @@
       <c r="W6" t="inlineStr">
         <is>
           <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>T-Deg-0047</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1202,7 +1187,7 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Owe Nilsson</t>
+          <t>Emilia Sundell</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
@@ -1210,18 +1195,14 @@
           <t>Emilia Sundell</t>
         </is>
       </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131521663</v>
+        <v>129678392</v>
       </c>
       <c r="B7" t="n">
-        <v>92308</v>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1229,37 +1210,41 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Holmtorp, Karlskoga, Vrm</t>
+          <t>Holmtorp, Vrm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>467244</v>
+        <v>467476</v>
       </c>
       <c r="R7" t="n">
-        <v>6572972</v>
+        <v>6572930</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1283,12 +1268,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1297,22 +1282,256 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Mattias Drejby</t>
+          <t>Emilia Sundell</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Mattias Drejby</t>
+          <t>Emilia Sundell</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>129896162</v>
+      </c>
+      <c r="B8" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Holmtorp, ONO om, Vrm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>467477</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6572930</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>T-Deg-0047</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-06-27</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-06-27</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Owe Nilsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Emilia Sundell</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>129678315</v>
+      </c>
+      <c r="B9" t="n">
+        <v>80477</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>229504</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Grynig filtlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Peltigera collina</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Schrad.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Holmtorp, Vrm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>467444</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6572961</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-06-27</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-06-27</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Emilia Sundell</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Emilia Sundell, Hannes Byström</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 73321-2021 artfynd.xlsx
+++ b/artfynd/A 73321-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -770,6 +775,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131521663</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -877,6 +887,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131507935</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -989,6 +1004,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131509684</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1095,6 +1115,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129678322</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1196,6 +1221,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129678393</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1297,6 +1327,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129678392</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1412,6 +1447,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129896162</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1532,8 +1572,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129678315</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>